--- a/documents/finance.xlsx
+++ b/documents/finance.xlsx
@@ -516,7 +516,6 @@
           <t>2022-01-27</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>157100</v>
       </c>
@@ -568,7 +567,6 @@
           <t>2024-03-07</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>132200</v>
       </c>
@@ -620,7 +618,6 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>94700</v>
       </c>
@@ -672,7 +669,6 @@
           <t>2024-02-16</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>110200</v>
       </c>
@@ -724,7 +720,6 @@
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>73300</v>
       </c>
@@ -776,7 +771,6 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>84000</v>
       </c>
@@ -828,7 +822,6 @@
           <t>2023-09-25</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>104400</v>
       </c>
@@ -880,7 +873,6 @@
           <t>2021-10-27</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>113200</v>
       </c>
@@ -932,7 +924,6 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>114100</v>
       </c>
@@ -984,7 +975,6 @@
           <t>2022-10-20</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>152900</v>
       </c>
@@ -1036,7 +1026,6 @@
           <t>2023-01-07</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>121000</v>
       </c>
@@ -1088,7 +1077,6 @@
           <t>2024-09-26</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>124700</v>
       </c>
@@ -1140,7 +1128,6 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>137200</v>
       </c>
@@ -1192,7 +1179,6 @@
           <t>2021-03-20</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>85500</v>
       </c>
@@ -1244,7 +1230,6 @@
           <t>2020-02-09</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>89800</v>
       </c>
@@ -1296,7 +1281,6 @@
           <t>2022-07-12</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>78800</v>
       </c>
@@ -1348,7 +1332,6 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>94800</v>
       </c>
@@ -1400,7 +1383,6 @@
           <t>2022-09-18</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>103000</v>
       </c>
@@ -1452,7 +1434,6 @@
           <t>2021-09-04</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>145100</v>
       </c>
@@ -1504,7 +1485,6 @@
           <t>2021-01-26</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>110800</v>
       </c>
@@ -1556,7 +1536,6 @@
           <t>2021-03-13</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>117400</v>
       </c>
@@ -1608,7 +1587,6 @@
           <t>2021-02-11</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>130800</v>
       </c>
@@ -1660,7 +1638,6 @@
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>85200</v>
       </c>
@@ -1712,7 +1689,6 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>142400</v>
       </c>
@@ -1764,7 +1740,6 @@
           <t>2021-01-27</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>116800</v>
       </c>
@@ -1816,7 +1791,6 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>95100</v>
       </c>
@@ -1868,7 +1842,6 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>107300</v>
       </c>
@@ -1920,7 +1893,6 @@
           <t>2024-03-19</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>109100</v>
       </c>
@@ -1972,7 +1944,6 @@
           <t>2022-03-24</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>96400</v>
       </c>
@@ -2024,7 +1995,6 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>76800</v>
       </c>
@@ -2076,7 +2046,6 @@
           <t>2019-04-05</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
         <v>124000</v>
       </c>
@@ -2128,7 +2097,6 @@
           <t>2020-11-10</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>104400</v>
       </c>
@@ -2180,7 +2148,6 @@
           <t>2022-02-20</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
         <v>92300</v>
       </c>
@@ -2232,7 +2199,6 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
         <v>83600</v>
       </c>
@@ -2284,7 +2250,6 @@
           <t>2019-05-09</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>93700</v>
       </c>
@@ -2336,7 +2301,6 @@
           <t>2022-09-04</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>88200</v>
       </c>
@@ -2388,7 +2352,6 @@
           <t>2022-10-17</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>83600</v>
       </c>
@@ -2440,7 +2403,6 @@
           <t>2021-04-02</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>114100</v>
       </c>
@@ -2492,7 +2454,6 @@
           <t>2019-02-21</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>117600</v>
       </c>
@@ -2544,7 +2505,6 @@
           <t>2019-12-08</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>120900</v>
       </c>
@@ -2596,7 +2556,6 @@
           <t>2021-07-28</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
         <v>78400</v>
       </c>
@@ -2648,7 +2607,6 @@
           <t>2024-05-11</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>89700</v>
       </c>
@@ -2700,7 +2658,6 @@
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>114600</v>
       </c>
@@ -2752,7 +2709,6 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
         <v>87300</v>
       </c>
@@ -2804,7 +2760,6 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
         <v>81200</v>
       </c>
@@ -2856,7 +2811,6 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
         <v>104900</v>
       </c>
@@ -2908,7 +2862,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
         <v>93800</v>
       </c>
@@ -2960,7 +2913,6 @@
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
         <v>136900</v>
       </c>
@@ -3012,7 +2964,6 @@
           <t>2018-12-09</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
         <v>150700</v>
       </c>
@@ -3064,7 +3015,6 @@
           <t>2022-11-27</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>112600</v>
       </c>
@@ -3116,7 +3066,6 @@
           <t>2024-01-16</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
         <v>86800</v>
       </c>
@@ -3168,7 +3117,6 @@
           <t>2022-03-16</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
         <v>97100</v>
       </c>
@@ -3220,7 +3168,6 @@
           <t>2024-04-26</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
         <v>97100</v>
       </c>
@@ -3272,7 +3219,6 @@
           <t>2022-12-14</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
         <v>158200</v>
       </c>
@@ -3324,7 +3270,6 @@
           <t>2023-05-13</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
         <v>107200</v>
       </c>
@@ -3376,7 +3321,6 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
         <v>118000</v>
       </c>
@@ -3428,7 +3372,6 @@
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
         <v>82600</v>
       </c>
@@ -3480,7 +3423,6 @@
           <t>2018-06-04</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
         <v>141500</v>
       </c>
@@ -3532,7 +3474,6 @@
           <t>2022-08-23</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
         <v>118500</v>
       </c>
@@ -3584,7 +3525,6 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>146100</v>
       </c>
@@ -3636,7 +3576,6 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>139000</v>
       </c>
@@ -3688,7 +3627,6 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
         <v>92000</v>
       </c>
@@ -3740,7 +3678,6 @@
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
         <v>94900</v>
       </c>
@@ -3792,7 +3729,6 @@
           <t>2020-04-19</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
         <v>137000</v>
       </c>
@@ -3844,7 +3780,6 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
         <v>125000</v>
       </c>
@@ -3896,7 +3831,6 @@
           <t>2021-04-14</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
         <v>135100</v>
       </c>
@@ -3948,7 +3882,6 @@
           <t>2023-02-12</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>113700</v>
       </c>
@@ -4000,7 +3933,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>70800</v>
       </c>
@@ -4052,7 +3984,6 @@
           <t>2019-03-02</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
         <v>125000</v>
       </c>
@@ -4104,7 +4035,6 @@
           <t>2025-06-19</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>109200</v>
       </c>
@@ -4156,7 +4086,6 @@
           <t>2022-06-28</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
         <v>104900</v>
       </c>
@@ -4208,7 +4137,6 @@
           <t>2022-01-22</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
         <v>109400</v>
       </c>
@@ -4260,7 +4188,6 @@
           <t>2023-10-03</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
         <v>115300</v>
       </c>
@@ -4312,7 +4239,6 @@
           <t>2024-05-08</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
         <v>89500</v>
       </c>
@@ -4364,7 +4290,6 @@
           <t>2022-06-27</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
         <v>140700</v>
       </c>
@@ -4416,7 +4341,6 @@
           <t>2022-05-19</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
         <v>91700</v>
       </c>
@@ -4468,7 +4392,6 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>119700</v>
       </c>
@@ -4520,7 +4443,6 @@
           <t>2022-03-27</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>97000</v>
       </c>
@@ -4572,7 +4494,6 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
         <v>97800</v>
       </c>
@@ -4624,7 +4545,6 @@
           <t>2023-02-03</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>100000</v>
       </c>
@@ -4676,7 +4596,6 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>97800</v>
       </c>
@@ -4728,7 +4647,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>85900</v>
       </c>
@@ -4780,7 +4698,6 @@
           <t>2025-05-17</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
         <v>109700</v>
       </c>
@@ -4832,7 +4749,6 @@
           <t>2022-05-05</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
         <v>106500</v>
       </c>
@@ -4884,7 +4800,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>102100</v>
       </c>
@@ -4936,7 +4851,6 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
         <v>117200</v>
       </c>
@@ -4988,7 +4902,6 @@
           <t>2023-03-28</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
         <v>113800</v>
       </c>
@@ -5040,7 +4953,6 @@
           <t>2025-06-11</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
         <v>68300</v>
       </c>
@@ -5092,7 +5004,6 @@
           <t>2024-04-04</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
         <v>89700</v>
       </c>
@@ -5144,7 +5055,6 @@
           <t>2023-10-12</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
         <v>123700</v>
       </c>
@@ -5196,7 +5106,6 @@
           <t>2019-01-18</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
         <v>117600</v>
       </c>
@@ -5248,7 +5157,6 @@
           <t>2019-11-28</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
         <v>153100</v>
       </c>
@@ -5300,7 +5208,6 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
         <v>137600</v>
       </c>
@@ -5352,7 +5259,6 @@
           <t>2023-03-06</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
         <v>86200</v>
       </c>
@@ -5404,7 +5310,6 @@
           <t>2021-02-21</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>158800</v>
       </c>
@@ -5456,7 +5361,6 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>123700</v>
       </c>
@@ -5508,7 +5412,6 @@
           <t>2019-12-09</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
         <v>98100</v>
       </c>
@@ -5560,7 +5463,6 @@
           <t>2022-03-02</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
         <v>89200</v>
       </c>
@@ -5612,7 +5514,6 @@
           <t>2023-03-10</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>114100</v>
       </c>
@@ -5664,7 +5565,6 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
         <v>152500</v>
       </c>
@@ -5716,7 +5616,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>103300</v>
       </c>
@@ -5768,7 +5667,6 @@
           <t>2021-08-19</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
         <v>104800</v>
       </c>
@@ -5820,7 +5718,6 @@
           <t>2021-06-23</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>116700</v>
       </c>
@@ -5872,7 +5769,6 @@
           <t>2023-07-08</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
         <v>108800</v>
       </c>
@@ -5924,7 +5820,6 @@
           <t>2021-02-28</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
         <v>133400</v>
       </c>
@@ -6088,7 +5983,6 @@
           <t>2021-08-09</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
         <v>108600</v>
       </c>
@@ -6150,7 +6044,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6206,7 +6100,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -6588,7 +6482,6 @@
           <t>2023-03-27</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
         <v>77800</v>
       </c>
@@ -6986,7 +6879,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -7042,7 +6935,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -7154,7 +7047,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -7210,7 +7103,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -7424,7 +7317,6 @@
           <t>2023-01-03</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
         <v>135200</v>
       </c>
@@ -7532,7 +7424,6 @@
           <t>2023-10-23</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
         <v>105300</v>
       </c>
@@ -7640,7 +7531,6 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
         <v>132000</v>
       </c>
@@ -7870,7 +7760,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -8140,7 +8030,6 @@
           <t>2024-02-28</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
         <v>85800</v>
       </c>
@@ -8258,7 +8147,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -8314,7 +8203,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -8482,7 +8371,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -8706,7 +8595,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -8818,7 +8707,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -9098,7 +8987,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -9602,7 +9491,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I172" t="n">
@@ -9770,7 +9659,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -10442,7 +10331,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I187" t="n">
@@ -10610,7 +10499,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I190" t="n">
@@ -10834,7 +10723,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I194" t="n">
@@ -11048,7 +10937,6 @@
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
       <c r="G198" t="n">
         <v>107500</v>
       </c>
@@ -11166,7 +11054,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I200" t="n">
@@ -11726,7 +11614,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I210" t="n">

--- a/documents/finance.xlsx
+++ b/documents/finance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:L217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,12 +516,17 @@
           <t>2022-01-27</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
       <c r="G2" t="n">
         <v>157100</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1230,12 +1235,17 @@
           <t>2020-02-09</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
       <c r="G16" t="n">
         <v>89800</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1281,12 +1291,17 @@
           <t>2022-07-12</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="G17" t="n">
         <v>78800</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1740,12 +1755,17 @@
           <t>2021-01-27</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="G26" t="n">
         <v>116800</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1944,12 +1964,17 @@
           <t>2022-03-24</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="G30" t="n">
         <v>96400</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2097,12 +2122,17 @@
           <t>2020-11-10</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="G33" t="n">
         <v>104400</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2250,12 +2280,17 @@
           <t>2019-05-09</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
       <c r="G36" t="n">
         <v>93700</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2556,12 +2591,17 @@
           <t>2021-07-28</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="G42" t="n">
         <v>78400</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2709,12 +2749,17 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
       <c r="G45" t="n">
         <v>87300</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -2811,12 +2856,17 @@
           <t>2023-06-15</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
       <c r="G47" t="n">
         <v>104900</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -2964,12 +3014,17 @@
           <t>2018-12-09</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
       <c r="G50" t="n">
         <v>150700</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3168,12 +3223,17 @@
           <t>2024-04-26</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="G54" t="n">
         <v>97100</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3270,12 +3330,17 @@
           <t>2023-05-13</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="G56" t="n">
         <v>107200</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3474,12 +3539,17 @@
           <t>2022-08-23</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
       <c r="G60" t="n">
         <v>118500</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -3831,12 +3901,17 @@
           <t>2021-04-14</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="G67" t="n">
         <v>135100</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -3882,12 +3957,17 @@
           <t>2023-02-12</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
       <c r="G68" t="n">
         <v>113700</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -3984,12 +4064,17 @@
           <t>2019-03-02</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
       <c r="G70" t="n">
         <v>125000</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4035,12 +4120,17 @@
           <t>2025-06-19</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
       <c r="G71" t="n">
         <v>109200</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4137,12 +4227,17 @@
           <t>2022-01-22</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
       <c r="G73" t="n">
         <v>109400</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4392,12 +4487,17 @@
           <t>2021-10-13</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
       <c r="G78" t="n">
         <v>119700</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -5208,12 +5308,17 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="G94" t="n">
         <v>137600</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -11685,6 +11790,312 @@
         </is>
       </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Eugene Reynolds</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2002-07-04</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>108400</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>3</v>
+      </c>
+      <c r="J212" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Dennis Moore</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1971-06-12</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Financial Analyst</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>78600</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Daniel Thomas</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1978-12-18</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>114500</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>3</v>
+      </c>
+      <c r="J214" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Aaron Cole</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1972-11-18</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Financial Analyst</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>87500</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Kevin Chavez</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1978-09-18</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Financial Analyst</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>79400</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>3</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Donna Butler</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1972-07-23</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Financial Analyst</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>86600</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>3</v>
+      </c>
+      <c r="J217" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
         <is>
           <t>White</t>
         </is>
